--- a/assessment_forms/001_risk_appetite_assessment_questionnaire--assessment_forms.xlsx
+++ b/assessment_forms/001_risk_appetite_assessment_questionnaire--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2173,24 +2173,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>risk_level_9_choices</t>
+          <t>risk_level_10_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>low</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2321,46 +2321,46 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme_highest</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>risk_level_10_choices</t>
+          <t>risk_level_11_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>risk_level_10_choices</t>
+          <t>risk_level_11_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2474,80 +2474,80 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme_highest</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>risk_level_11_choices</t>
+          <t>risk_level_12_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>risk_level_11_choices</t>
+          <t>risk_level_12_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>risk_level_11_choices</t>
+          <t>risk_level_12_choices</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>risk_level_11_choices</t>
+          <t>risk_level_12_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2627,114 +2627,114 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extreme_highest</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>risk_level_12_choices</t>
+          <t>risk_level_13_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>risk_level_12_choices</t>
+          <t>risk_level_13_choices</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>risk_level_12_choices</t>
+          <t>risk_level_13_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>risk_level_12_choices</t>
+          <t>risk_level_13_choices</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>risk_level_12_choices</t>
+          <t>risk_level_13_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>risk_level_12_choices</t>
+          <t>risk_level_13_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2780,148 +2780,148 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extreme_highest</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>risk_level_13_choices</t>
+          <t>risk_level_14_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
@@ -2933,155 +2933,155 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>extreme_highest</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>extreme_higher</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_15_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3091,517 +3091,160 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>low</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>risk_level_14_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>extreme_highest</t>
+          <t>medium</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>very high</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extremely high</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>highest</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>very_high</t>
+          <t>highest</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extreme_high</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>extremely_high</t>
+          <t>extreme high</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extreme_higher</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>highest</t>
+          <t>extreme higher</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>risk_level_15_choices</t>
+          <t>risk_level_16_choices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>extreme_high</t>
+          <t>extreme_highest</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>extreme_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>risk_level_15_choices</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>extreme_higher</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>extreme_higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>risk_level_15_choices</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>risk_level_15_choices</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>risk_level_15_choices</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>risk_level_15_choices</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>risk_level_15_choices</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>very_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>extremely_high</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>extremely_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>highest</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>extreme_high</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>extreme_high</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>extreme_higher</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>extreme_higher</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>risk_level_16_choices</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>extreme_highest</t>
+          <t>extreme highest</t>
         </is>
       </c>
     </row>
